--- a/diseases/d125/2026-2029.xlsx
+++ b/diseases/d125/2026-2029.xlsx
@@ -11029,12 +11029,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -11068,81 +11068,95 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>0.5046235431273006</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_VRE</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS62" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ62" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_VRE</t>
+        </is>
+      </c>
       <c r="AT62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -11169,17 +11183,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -11204,7 +11218,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -11213,81 +11227,170 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>54</v>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_VRE</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_VRE</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Vancomycinresistenta enterokocker</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Organism and infection or colonization scope retained at source-series level.</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN63" t="b">
+        <v>1</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS63" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ63" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_VRE</t>
+        </is>
+      </c>
       <c r="AT63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -11349,7 +11452,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -11358,13 +11461,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -11494,7 +11597,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -11503,13 +11606,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -11609,12 +11712,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -11639,104 +11742,90 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N66" t="n">
+        <v>1</v>
+      </c>
+      <c r="O66" t="n">
+        <v>1</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP66" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr"/>
+      <c r="AT66" t="n">
         <v>0</v>
       </c>
-      <c r="O66" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_803_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP66" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ66" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS66" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_803_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT66" t="n">
-        <v>1</v>
-      </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11763,212 +11852,516 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>万古霉素耐药性</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>1</v>
+      </c>
+      <c r="O67" t="n">
+        <v>1</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP67" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr"/>
+      <c r="AT67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV67" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA67" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB67" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC67" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>vancomycin-resistance</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>万古霉素耐药性</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_803_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP68" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ68" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_803_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV68" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA68" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB68" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC68" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>vancomycin-resistance</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>D125</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Vancomycin resistance</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
         <is>
           <t>万古霉素耐药性</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N67" t="n">
+      <c r="N69" t="n">
         <v>0</v>
       </c>
-      <c r="O67" t="n">
+      <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="U69" t="inlineStr">
         <is>
           <t>SER_NO_FHI_803_MONTHLY</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr">
+      <c r="V69" t="inlineStr">
         <is>
           <t>SER_NO_FHI_803_MONTHLY</t>
         </is>
       </c>
-      <c r="W67" t="inlineStr">
+      <c r="W69" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>Resistent enterokokk</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
+      <c r="Y69" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
+      <c r="Z69" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA67" t="inlineStr">
+      <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
+      <c r="AB69" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
+      <c r="AC69" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD67" t="inlineStr">
+      <c r="AD69" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE67" t="inlineStr">
+      <c r="AE69" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF67" t="inlineStr">
+      <c r="AF69" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG67" t="inlineStr">
+      <c r="AG69" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH67" t="inlineStr">
+      <c r="AH69" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI67" t="inlineStr">
+      <c r="AI69" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ67" t="inlineStr">
+      <c r="AJ69" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK67" t="inlineStr">
+      <c r="AK69" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS resistant-enterococcus category.</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
+      <c r="AM69" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN67" t="b">
+      <c r="AN69" t="b">
         <v>1</v>
       </c>
-      <c r="AO67" t="inlineStr">
+      <c r="AO69" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP67" t="inlineStr">
+      <c r="AP69" t="inlineStr">
         <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ67" t="inlineStr">
+      <c r="AQ69" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AS67" t="inlineStr">
+      <c r="AS69" t="inlineStr">
         <is>
           <t>SER_NO_FHI_803_MONTHLY</t>
         </is>
       </c>
-      <c r="AT67" t="n">
+      <c r="AT69" t="n">
         <v>1</v>
       </c>
-      <c r="AU67" t="inlineStr">
+      <c r="AU69" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
-      <c r="AV67" t="inlineStr">
+      <c r="AV69" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW67" t="inlineStr">
+      <c r="AW69" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
+      <c r="AX69" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY67" t="inlineStr">
+      <c r="AY69" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
+      <c r="AZ69" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA67" t="inlineStr">
+      <c r="BA69" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB67" t="inlineStr">
+      <c r="BB69" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC67" t="inlineStr">
+      <c r="BC69" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -12090,7 +12483,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10">
@@ -12100,7 +12493,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11">
@@ -12120,7 +12513,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -12152,7 +12545,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>676</v>
+        <v>730</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d125/2026-2029.xlsx
+++ b/diseases/d125/2026-2029.xlsx
@@ -12002,12 +12002,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -12032,104 +12032,90 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N68" t="n">
+        <v>1</v>
+      </c>
+      <c r="O68" t="n">
+        <v>1</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP68" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr"/>
+      <c r="AT68" t="n">
         <v>0</v>
       </c>
-      <c r="O68" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" t="n">
-        <v>0</v>
-      </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_803_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP68" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ68" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS68" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_803_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT68" t="n">
-        <v>1</v>
-      </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12156,7 +12142,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -12205,98 +12191,23 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U69" t="inlineStr">
         <is>
           <t>SER_NO_FHI_803_MONTHLY</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_803_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>Resistent enterokokk</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD69" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE69" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF69" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG69" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS resistant-enterococcus category.</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN69" t="b">
-        <v>1</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -12362,6 +12273,240 @@
         </is>
       </c>
       <c r="BC69" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>vancomycin-resistance</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>万古霉素耐药性</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_803_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_803_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Resistent enterokokk</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS resistant-enterococcus category.</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN70" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP70" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ70" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_803_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV70" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA70" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB70" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC70" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -12483,7 +12628,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10">
@@ -12493,7 +12638,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11">
@@ -12545,7 +12690,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d125/2026-2029.xlsx
+++ b/diseases/d125/2026-2029.xlsx
@@ -10675,13 +10675,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O60" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R60" t="n">
-        <v>0.283036132127281</v>
+        <v>0.3007258903852361</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -10834,10 +10834,10 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O61" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -12186,13 +12186,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -12345,10 +12345,10 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U70" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>731</v>
+        <v>733</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d125/2026-2029.xlsx
+++ b/diseases/d125/2026-2029.xlsx
@@ -12512,6 +12512,151 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>vancomycin-resistance</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>万古霉素耐药性</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP71" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr"/>
+      <c r="AT71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV71" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA71" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB71" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC71" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12545,7 +12690,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -12628,7 +12773,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
@@ -12638,7 +12783,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d125/2026-2029.xlsx
+++ b/diseases/d125/2026-2029.xlsx
@@ -12186,13 +12186,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O69" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R69" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.1415180660636405</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -12345,10 +12345,10 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O70" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U70" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>733</v>
+        <v>740</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d125/2026-2029.xlsx
+++ b/diseases/d125/2026-2029.xlsx
@@ -12186,13 +12186,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="O69" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="R69" t="n">
-        <v>0.1415180660636405</v>
+        <v>0.2299668573534158</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -12345,10 +12345,10 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="O70" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="U70" t="inlineStr">
         <is>
@@ -12652,6 +12652,151 @@
         </is>
       </c>
       <c r="BC71" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>vancomycin-resistance</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>万古霉素耐药性</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP72" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr"/>
+      <c r="AT72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV72" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA72" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB72" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC72" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -12690,7 +12835,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -12773,7 +12918,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10">
@@ -12783,7 +12928,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11">
@@ -12835,7 +12980,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>740</v>
+        <v>745</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d125/2026-2029.xlsx
+++ b/diseases/d125/2026-2029.xlsx
@@ -12802,6 +12802,151 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>vancomycin-resistance</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>万古霉素耐药性</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP73" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr"/>
+      <c r="AT73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV73" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA73" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC73" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12835,7 +12980,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -12918,7 +13063,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10">
@@ -12928,7 +13073,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d125/2026-2029.xlsx
+++ b/diseases/d125/2026-2029.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN44" t="b">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN52" t="b">
@@ -10675,13 +10675,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O60" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R60" t="n">
-        <v>0.3007258903852361</v>
+        <v>0.3184156486431911</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -10834,10 +10834,10 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O61" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12186,13 +12186,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="O69" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="R69" t="n">
-        <v>0.2299668573534158</v>
+        <v>0.3537951651591013</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -12345,10 +12345,10 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="O70" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="U70" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -13125,7 +13125,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d125/2026-2029.xlsx
+++ b/diseases/d125/2026-2029.xlsx
@@ -12947,6 +12947,151 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>vancomycin-resistance</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>万古霉素耐药性</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP74" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr"/>
+      <c r="AT74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV74" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA74" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB74" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC74" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12980,7 +13125,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -13063,7 +13208,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10">
@@ -13073,7 +13218,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d125/2026-2029.xlsx
+++ b/diseases/d125/2026-2029.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN44" t="b">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN52" t="b">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12186,13 +12186,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O69" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="R69" t="n">
-        <v>0.3537951651591013</v>
+        <v>0.4245541981909216</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -12345,10 +12345,10 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O70" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="U70" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -12540,12 +12540,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -12579,81 +12579,95 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>0.5046235431273006</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_VRE</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS71" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ71" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_VRE</t>
+        </is>
+      </c>
       <c r="AT71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -12680,17 +12694,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -12715,7 +12729,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -12724,81 +12738,170 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>54</v>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_VRE</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_VRE</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Vancomycinresistenta enterokocker</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Organism and infection or colonization scope retained at source-series level.</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN72" t="b">
+        <v>1</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS72" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_VRE</t>
+        </is>
+      </c>
       <c r="AT72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -12860,7 +12963,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -13005,7 +13108,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -13089,6 +13192,689 @@
       <c r="BC74" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>vancomycin-resistance</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>万古霉素耐药性</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP75" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr"/>
+      <c r="AT75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV75" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA75" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB75" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC75" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>vancomycin-resistance</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>万古霉素耐药性</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP76" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr"/>
+      <c r="AT76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV76" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA76" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB76" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC76" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>vancomycin-resistance</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>万古霉素耐药性</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>3</v>
+      </c>
+      <c r="O77" t="n">
+        <v>3</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0.05306927477386519</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_803_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_803_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV77" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA77" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC77" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>vancomycin-resistance</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>万古霉素耐药性</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>3</v>
+      </c>
+      <c r="O78" t="n">
+        <v>3</v>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_803_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_803_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Resistent enterokokk</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS resistant-enterococcus category.</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN78" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_803_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -13125,7 +13911,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -13208,7 +13994,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10">
@@ -13218,7 +14004,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11">
@@ -13238,7 +14024,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -13270,7 +14056,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>753</v>
+        <v>814</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d125/2026-2029.xlsx
+++ b/diseases/d125/2026-2029.xlsx
@@ -12186,13 +12186,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O69" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R69" t="n">
-        <v>0.4245541981909216</v>
+        <v>0.4422439564488765</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -12345,10 +12345,10 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O70" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U70" t="inlineStr">
         <is>
@@ -13552,13 +13552,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R77" t="n">
-        <v>0.05306927477386519</v>
+        <v>0.07075903303182025</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -13711,10 +13711,10 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U78" t="inlineStr">
         <is>
@@ -13875,6 +13875,151 @@
       <c r="BC78" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>vancomycin-resistance</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>D125</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Vancomycin resistance</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>万古霉素耐药性</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr"/>
+      <c r="AT79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -13911,7 +14056,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -13994,7 +14139,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10">
@@ -14004,7 +14149,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11">
@@ -14056,7 +14201,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>814</v>
+        <v>816</v>
       </c>
     </row>
     <row r="16">
